--- a/output/Shandong/淄博市_news.xlsx
+++ b/output/Shandong/淄博市_news.xlsx
@@ -551,9 +551,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>True</t>
@@ -565,14 +563,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11274</v>
+        <v>11820</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ce2a7d851eb94d80850ac36dca45cd37/detail</t>
@@ -621,9 +617,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>True</t>
@@ -635,14 +629,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11173</v>
+        <v>11724</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ac7aededc8de492bb87625b37c495af2/detail</t>
@@ -691,9 +683,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>True</t>
@@ -705,14 +695,12 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>11240</v>
+        <v>11811</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b6414d46f1e64b06af2947096426e9b0/detail</t>
@@ -761,9 +749,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>True</t>
@@ -775,14 +761,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>11344</v>
+        <v>11896</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/af32ed868d3d4687bf76b27b870849b7/detail</t>
@@ -831,9 +815,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>True</t>
@@ -845,14 +827,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11044</v>
+        <v>11583</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/26cb65f16ff5456d9c8a347ca2688064/detail</t>
@@ -901,9 +881,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>True</t>
@@ -915,14 +893,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10367</v>
+        <v>10908</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/cfbcc0f9751041b280e644da42352521/detail</t>
@@ -971,9 +947,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>True</t>
@@ -985,14 +959,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10980</v>
+        <v>11523</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/0d22443b6b8a4f8fb1ebae1f0e307491/detail</t>
@@ -1041,9 +1013,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1055,14 +1025,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10820</v>
+        <v>11365</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/aa38bf08e69242c7961345d443e810ee/detail</t>
@@ -1111,9 +1079,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>True</t>
@@ -1125,14 +1091,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>10728</v>
+        <v>11272</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/da79c4cb8d96458789f7bc7770162f5d/detail</t>
@@ -1177,9 +1141,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>True</t>
@@ -1191,14 +1153,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>16325</v>
+        <v>16864</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/e53b28c3b399442c8600d140be6f7e38/detail</t>
@@ -1247,9 +1207,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>True</t>
@@ -1261,14 +1219,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5904</v>
+        <v>5916</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5772456c6ac64b459120d9cc2d7f5236/detail</t>
@@ -1284,22 +1240,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中职学校专业设置信息_分页查询</t>
+          <t>建筑工程施工许可证核发_分页查询</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>城建住房</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>中职学校专业设置信息_分页查询</t>
+          <t>建筑工程施工许可证核发_分页查询</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>淄博市张店区</t>
+          <t>淄博市高新区</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1317,9 +1273,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>True</t>
@@ -1331,17 +1285,15 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6093</v>
+        <v>6269</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/dee7d736aeef42cdb1d8713844b138c9/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5fa5c770d7124471a01809ec2fef8d79/detail</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1354,22 +1306,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>建筑工程施工许可证核发_分页查询</t>
+          <t>中职学校专业设置信息_分页查询</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>城建住房</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>建筑工程施工许可证核发_分页查询</t>
+          <t>中职学校专业设置信息_分页查询</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>淄博市高新区</t>
+          <t>淄博市张店区</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1387,9 +1339,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>True</t>
@@ -1401,17 +1351,15 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6258</v>
+        <v>6097</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5fa5c770d7124471a01809ec2fef8d79/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/dee7d736aeef42cdb1d8713844b138c9/detail</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1457,9 +1405,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>True</t>
@@ -1471,14 +1417,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6363</v>
+        <v>6375</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ddc28e8c7ba34dbca449968c79b4193d/detail</t>
@@ -1527,9 +1471,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>True</t>
@@ -1541,14 +1483,12 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6091</v>
+        <v>6099</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/e6551b33143844cd9b79dc014a0400a3/detail</t>
@@ -1597,9 +1537,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>True</t>
@@ -1611,14 +1549,12 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6295</v>
+        <v>6302</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f9736347c14d4a3f90149d8104dd5988/detail</t>
@@ -1667,9 +1603,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>True</t>
@@ -1681,14 +1615,12 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5798</v>
+        <v>5804</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/05bde271cf4c4045a2353f1b5ef9c122/detail</t>
@@ -1737,9 +1669,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>True</t>
@@ -1751,14 +1681,12 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6508</v>
+        <v>6708</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d8b731ce086e453697cf1a1f7961101e/detail</t>
@@ -1807,9 +1735,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>True</t>
@@ -1821,14 +1747,12 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6279</v>
+        <v>6290</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ca5a8c8e69ec4bc2b306cadf56332b96/detail</t>
@@ -1877,9 +1801,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>True</t>
@@ -1891,14 +1813,12 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/9290c474c80945bdba2b2acf0caf659c/detail</t>
@@ -1947,9 +1867,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>True</t>
@@ -1961,14 +1879,12 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/4429b546e1ee436baed308b0781200eb/detail</t>
@@ -2017,9 +1933,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>True</t>
@@ -2031,14 +1945,12 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/07fa7cc207224f8781f674d72070d7c4/detail</t>
@@ -2087,9 +1999,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>True</t>
@@ -2101,14 +2011,12 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/71b8d8af0ecd416a8d2220df8cc42729/detail</t>
@@ -2157,9 +2065,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>True</t>
@@ -2171,14 +2077,12 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8bfcc03c74a1433e8c38035535f208ce/detail</t>
@@ -2227,9 +2131,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>True</t>
@@ -2241,14 +2143,12 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/fc97d93e6ff44dca886ac71d2de71792/detail</t>
@@ -2297,9 +2197,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>True</t>
@@ -2311,14 +2209,12 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/12ed4bffccc84518bf298f2b7969a332/detail</t>
@@ -2367,9 +2263,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>True</t>
@@ -2381,14 +2275,12 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8341</v>
+        <v>8591</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/da1b07a5ad56427eaa9372d56b9c932d/detail</t>
@@ -2437,9 +2329,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>True</t>
@@ -2451,14 +2341,12 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/dcf9a2d8fcfe49a99db9d57a8dae6950/detail</t>
@@ -2507,9 +2395,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>True</t>
@@ -2521,14 +2407,12 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/095677e2741e40b28a5edf72af5a2a5b/detail</t>
@@ -2577,9 +2461,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>True</t>
@@ -2591,14 +2473,12 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/4b112230ede947c4a0b6e1fef567f87c/detail</t>
@@ -2647,9 +2527,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>True</t>
@@ -2661,14 +2539,12 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ac0d6b1ab6c44f5081e176d7434e0daa/detail</t>
@@ -2717,9 +2593,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>True</t>
@@ -2731,14 +2605,12 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>365</v>
+        <v>585</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/a37051e076d34551b37d3fe801d73ed5/detail</t>
@@ -2787,9 +2659,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>True</t>
@@ -2801,14 +2671,12 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f6ddd08c4bff4ed28a10b0e81ddc1df9/detail</t>
@@ -2857,9 +2725,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>True</t>
@@ -2871,14 +2737,12 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>346</v>
+        <v>555</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/86568188b5e242fcaa9c423bc4820582/detail</t>
@@ -2927,9 +2791,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>True</t>
@@ -2941,14 +2803,12 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/bd5f6bf764414001b18193fd2fdc6e94/detail</t>
@@ -2997,9 +2857,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>True</t>
@@ -3011,14 +2869,12 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b777a3abae754bc6ba3fe11f86c2645d/detail</t>
@@ -3067,9 +2923,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>True</t>
@@ -3081,14 +2935,12 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>389</v>
+        <v>586</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/02dda492c7fc41549263cfc298d1d801/detail</t>
@@ -3137,9 +2989,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>True</t>
@@ -3151,14 +3001,12 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/9e8b1fd08ee44eef93850594312d8204/detail</t>
@@ -3207,9 +3055,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>True</t>
@@ -3221,14 +3067,12 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b4ed1c7cddd74f508de6271da9a40b99/detail</t>
@@ -3277,9 +3121,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>True</t>
@@ -3291,14 +3133,12 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8b8877d8f4cf445dbdfcbebf0de8df0a/detail</t>
@@ -3347,9 +3187,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>True</t>
@@ -3361,14 +3199,12 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/c1cd95fd75964167a4bfd3f9246a0c92/detail</t>
@@ -3417,9 +3253,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>True</t>
@@ -3431,14 +3265,12 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5faa68fc18d740df8618af2aca79582d/detail</t>
@@ -3487,9 +3319,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>True</t>
@@ -3501,14 +3331,12 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/dbbb89a98b154c21a1ceed2b0bad0797/detail</t>
@@ -3557,9 +3385,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>True</t>
@@ -3571,14 +3397,12 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/38f3f8b0346d45869e6da777939ed90f/detail</t>
@@ -3627,9 +3451,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>True</t>
@@ -3641,14 +3463,12 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2400</v>
+        <v>2409</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d21fcd2a882843d0b037008721e83d99/detail</t>
@@ -3697,9 +3517,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>True</t>
@@ -3711,14 +3529,12 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/478e3a47a49649e889b0da1f87eee497/detail</t>
@@ -3767,9 +3583,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>True</t>
@@ -3781,14 +3595,12 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/a530cc060cba489f930144c289f61ec1/detail</t>
@@ -3837,9 +3649,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>True</t>
@@ -3851,14 +3661,12 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/4b7619cc43744b9c82a1c418aaad2a60/detail</t>
@@ -3907,9 +3715,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>True</t>
@@ -3921,14 +3727,12 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8fba3b7148604d9aba4f85c5e5a73eaa/detail</t>
@@ -3973,9 +3777,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>True</t>
@@ -3987,14 +3789,12 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1831</v>
+        <v>2039</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/bc1831472f9746d183adba74ab10e5d0/detail</t>
@@ -4043,9 +3843,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>True</t>
@@ -4057,14 +3855,12 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>5955</v>
+        <v>5957</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b271d7a9b8dc4a06af23cd8491443fe8/detail</t>
@@ -4113,9 +3909,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>True</t>
@@ -4127,14 +3921,12 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5212</v>
+        <v>5217</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/063b278b907f419f9442345e236b0e60/detail</t>
@@ -4183,9 +3975,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>True</t>
@@ -4197,14 +3987,12 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>15111</v>
+        <v>15115</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/1feecf7218f14488b1e4251d69bd59a2/detail</t>
@@ -4253,9 +4041,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>True</t>
@@ -4267,14 +4053,12 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>6744</v>
+        <v>6748</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/2367e012a2404c659ba0278c8be5d234/detail</t>
@@ -4323,9 +4107,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>True</t>
@@ -4337,14 +4119,12 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>6396</v>
+        <v>6403</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/2daa2a3ac0a14b88ad6eb3c29bfb01c7/detail</t>
@@ -4393,9 +4173,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>True</t>
@@ -4407,14 +4185,12 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>9672</v>
+        <v>9678</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/3e89ff9d6edd4ce38d1ef13284993696/detail</t>
@@ -4463,9 +4239,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>True</t>
@@ -4477,14 +4251,12 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>8945</v>
+        <v>8948</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/3f8682b4b0b24edebf5d00b248fa2ec2/detail</t>
@@ -4533,9 +4305,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>True</t>
@@ -4547,14 +4317,12 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>7258</v>
+        <v>7263</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/466d04b596184e78a0da382891eab97e/detail</t>
@@ -4570,27 +4338,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>危险化学品经营许可证核发信息分页查询服务</t>
+          <t>制定和调整相关财政补贴政策信息分页查询服务</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>危险化学品经营许可证核发信息分页查询服务</t>
+          <t>制定和调整相关财政补贴政策信息分页查询服务</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>淄博市高青县</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2018-12-21</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4603,9 +4371,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>True</t>
@@ -4617,17 +4383,15 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>5811</v>
+        <v>7586</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7c2588a5e30c4cca8e897e197c5a3c91/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5d5ecab86bd049709b9e76cdc3fdbd74/detail</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -4640,17 +4404,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>户外广告设置许可信息数据量查询服务</t>
+          <t>职业卫生检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>户外广告设置许可信息数据量查询服务</t>
+          <t>职业卫生检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4660,7 +4424,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4670,12 +4434,10 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>True</t>
@@ -4687,17 +4449,15 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>5387</v>
+        <v>6155</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7e6b397fb17645748e230181ee1b3806/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/60f4e782111640d590d66ee8c2d5f4ac/detail</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -4710,17 +4470,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>危险化学品企业重大危险源备案信息数据量查询服务</t>
+          <t>蛋鸡规模养殖场基本信息分页查询服务</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>危险化学品企业重大危险源备案信息数据量查询服务</t>
+          <t>蛋鸡规模养殖场基本信息分页查询服务</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4743,9 +4503,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>True</t>
@@ -4757,17 +4515,15 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>5212</v>
+        <v>6931</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/063b278b907f419f9442345e236b0e60/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/613a6011f5e246db95b40d891fee6262/detail</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -4780,17 +4536,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>淄川区金牌工匠评选信息数据量查询服务</t>
+          <t>环卫基础设施信息分页查询服务</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>淄川区金牌工匠评选信息数据量查询服务</t>
+          <t>环卫基础设施信息分页查询服务</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4800,7 +4556,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4813,9 +4569,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>True</t>
@@ -4827,17 +4581,15 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3787</v>
+        <v>6879</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/dd7666e66d334552af1ca794433e4504/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/65c94fd69bdb44db98303da39178cd23/detail</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -4850,17 +4602,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>旅行社信息数据量查询服务</t>
+          <t>烟花爆竹经营（零售）许可证核发信息数据量查询服务</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>旅行社信息数据量查询服务</t>
+          <t>烟花爆竹经营（零售）许可证核发信息数据量查询服务</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4870,7 +4622,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4883,9 +4635,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>True</t>
@@ -4897,17 +4647,15 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5040</v>
+        <v>7680</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e1357d237eea40f2b5596d24b3010f35/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/6f7467c865a64b088f63f250e8de1d8e/detail</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -4920,7 +4668,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>全区新增签约项目汇总表信息数据量查询服务</t>
+          <t>全区新增签约项目汇总表信息分页查询服务</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4930,7 +4678,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>全区新增签约项目汇总表信息数据量查询服务</t>
+          <t>全区新增签约项目汇总表信息分页查询服务</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4953,9 +4701,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>True</t>
@@ -4967,17 +4713,15 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>31053</v>
+        <v>30472</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e59fe5aa5663443d9156688df26d4919/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/737b398556114d9fb6852be69624c725/detail</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -4990,17 +4734,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>淄川区各级畜禽养殖示范场名单信息分页查询服务</t>
+          <t>货运经营者没有采取货物脱落扬撒处罚信息数据量查询服务</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>淄川区各级畜禽养殖示范场名单信息分页查询服务</t>
+          <t>货运经营者没有采取货物脱落扬撒处罚信息数据量查询服务</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5023,9 +4767,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>True</t>
@@ -5037,17 +4779,15 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>312</v>
+        <v>6567</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e78d77e185414874b6f768a8a8da800e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/73bac93ac848433695ae7f592ac963b8/detail</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -5060,27 +4800,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>互联网上网服务营业场所经营监督检查信息分页查询服务</t>
+          <t>危险化学品经营许可证核发信息分页查询服务</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>互联网上网服务营业场所经营监督检查信息分页查询服务</t>
+          <t>危险化学品经营许可证核发信息分页查询服务</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市高青县</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2018-12-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5093,9 +4833,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>True</t>
@@ -5107,17 +4845,15 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1236</v>
+        <v>5817</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f34e5919e6b84c1e9d3c62175b7243d0/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7c2588a5e30c4cca8e897e197c5a3c91/detail</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -5130,17 +4866,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>招聘会信息数据量查询服务</t>
+          <t>户外广告设置许可信息数据量查询服务</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>公共安全</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>招聘会信息数据量查询服务</t>
+          <t>户外广告设置许可信息数据量查询服务</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5150,7 +4886,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5163,9 +4899,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>True</t>
@@ -5177,17 +4911,15 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>192</v>
+        <v>5392</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f4bacf41196146bf8f297bf85a933fc6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7e6b397fb17645748e230181ee1b3806/detail</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5200,17 +4932,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>淄川区日间照料中心名单信息数据量查询服务</t>
+          <t>畜牧业项目专家库人员名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>淄川区日间照料中心名单信息数据量查询服务</t>
+          <t>畜牧业项目专家库人员名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5233,9 +4965,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>True</t>
@@ -5247,17 +4977,15 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>653</v>
+        <v>5910</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f94292f8335e47b28852451b95d52f3e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/86342dc141804c8b9655f89e5b7bb3d9/detail</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -5270,17 +4998,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>环卫基础设施信息分页查询服务</t>
+          <t>劳务派遣机构资格行政许可信息数据量查询服务</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>环卫基础设施信息分页查询服务</t>
+          <t>劳务派遣机构资格行政许可信息数据量查询服务</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5290,7 +5018,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5303,9 +5031,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>True</t>
@@ -5317,17 +5043,15 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>6873</v>
+        <v>5122</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/65c94fd69bdb44db98303da39178cd23/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9888da8905f4442792681c9ff90f4fec/detail</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -5340,7 +5064,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>烟花爆竹经营（零售）许可证核发信息数据量查询服务</t>
+          <t>安全生产检查信息分页查询服务</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5350,7 +5074,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>烟花爆竹经营（零售）许可证核发信息数据量查询服务</t>
+          <t>安全生产检查信息分页查询服务</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5360,7 +5084,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5373,9 +5097,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>True</t>
@@ -5387,17 +5109,15 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>7675</v>
+        <v>5023</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/6f7467c865a64b088f63f250e8de1d8e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9c3f14e540e84f109bd7dc523d1b36a1/detail</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -5410,27 +5130,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>全区新增签约项目汇总表信息分页查询服务</t>
+          <t>畜禽生产统计信息分页查询服务</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>全区新增签约项目汇总表信息分页查询服务</t>
+          <t>畜禽生产统计信息分页查询服务</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>淄博市博山区</t>
+          <t>淄博市临淄区</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018-11-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5440,12 +5160,10 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>True</t>
@@ -5457,17 +5175,15 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>30220</v>
+        <v>3987</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/737b398556114d9fb6852be69624c725/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9fd6d967f8d8416d9ff2e3e5ee3aea45/detail</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -5480,27 +5196,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>货运经营者没有采取货物脱落扬撒处罚信息数据量查询服务</t>
+          <t>社会民生事业和城市基础设施类投资项目信息分页查询服务</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>货运经营者没有采取货物脱落扬撒处罚信息数据量查询服务</t>
+          <t>社会民生事业和城市基础设施类投资项目信息分页查询服务</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市临淄区</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5510,12 +5226,10 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>True</t>
@@ -5527,17 +5241,15 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>6559</v>
+        <v>7257</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/73bac93ac848433695ae7f592ac963b8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a77173c46d1542b585a82f4a22de7906/detail</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -5550,27 +5262,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>危险化学品经营许可证核发信息分页查询服务</t>
+          <t>社会民生事业和城市基础设施类投资项目信息数据量查询服务</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>危险化学品经营许可证核发信息分页查询服务</t>
+          <t>社会民生事业和城市基础设施类投资项目信息数据量查询服务</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>淄博市高青县</t>
+          <t>淄博市临淄区</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2018-12-21</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5580,12 +5292,10 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>True</t>
@@ -5597,17 +5307,15 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>5811</v>
+        <v>8153</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7c2588a5e30c4cca8e897e197c5a3c91/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ae3bbbf85efe4993a911e9ca2484c8f8/detail</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -5620,17 +5328,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>户外广告设置许可信息数据量查询服务</t>
+          <t>取水许可审批信息分页查询服务</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>户外广告设置许可信息数据量查询服务</t>
+          <t>取水许可审批信息分页查询服务</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5640,7 +5348,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5650,12 +5358,10 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>True</t>
@@ -5667,17 +5373,15 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>5387</v>
+        <v>6113</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7e6b397fb17645748e230181ee1b3806/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b1c70df090b64ef59c42de4894f4adb0/detail</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -5723,9 +5427,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>True</t>
@@ -5737,14 +5439,12 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3909</v>
+        <v>3914</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/be9c4f726f46477d81821330528dc63d/detail</t>
@@ -5793,9 +5493,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>True</t>
@@ -5807,14 +5505,12 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3933</v>
+        <v>3941</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ca09e015c6964a8484b290bea1cdbc3c/detail</t>
@@ -5863,9 +5559,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>True</t>
@@ -5877,14 +5571,12 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>5094</v>
+        <v>5099</v>
       </c>
       <c r="M78" t="n">
         <v>1</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d168c08bcd7744f292307c063ad57375/detail</t>
@@ -5900,17 +5592,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>安全生产检查信息分页查询服务</t>
+          <t>淄川区金牌工匠评选信息数据量查询服务</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>安全生产检查信息分页查询服务</t>
+          <t>淄川区金牌工匠评选信息数据量查询服务</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5920,7 +5612,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5933,9 +5625,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>True</t>
@@ -5947,17 +5637,15 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>5019</v>
+        <v>3793</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9c3f14e540e84f109bd7dc523d1b36a1/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/dd7666e66d334552af1ca794433e4504/detail</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -5970,27 +5658,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>畜禽生产统计信息分页查询服务</t>
+          <t>旅行社信息数据量查询服务</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>畜禽生产统计信息分页查询服务</t>
+          <t>旅行社信息数据量查询服务</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>淄博市临淄区</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2018-11-26</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6000,12 +5688,10 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>True</t>
@@ -6017,17 +5703,15 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3981</v>
+        <v>5051</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9fd6d967f8d8416d9ff2e3e5ee3aea45/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e1357d237eea40f2b5596d24b3010f35/detail</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -6040,27 +5724,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>社会民生事业和城市基础设施类投资项目信息分页查询服务</t>
+          <t>全区新增签约项目汇总表信息数据量查询服务</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>社会民生事业和城市基础设施类投资项目信息分页查询服务</t>
+          <t>全区新增签约项目汇总表信息数据量查询服务</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>淄博市临淄区</t>
+          <t>淄博市博山区</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6070,12 +5754,10 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>True</t>
@@ -6087,17 +5769,15 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>7246</v>
+        <v>31307</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a77173c46d1542b585a82f4a22de7906/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e59fe5aa5663443d9156688df26d4919/detail</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -6110,27 +5790,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>社会民生事业和城市基础设施类投资项目信息数据量查询服务</t>
+          <t>淄川区各级畜禽养殖示范场名单信息分页查询服务</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>社会民生事业和城市基础设施类投资项目信息数据量查询服务</t>
+          <t>淄川区各级畜禽养殖示范场名单信息分页查询服务</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>淄博市临淄区</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6140,12 +5820,10 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>True</t>
@@ -6157,17 +5835,15 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>8143</v>
+        <v>321</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ae3bbbf85efe4993a911e9ca2484c8f8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e78d77e185414874b6f768a8a8da800e/detail</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -6180,17 +5856,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>取水许可审批信息分页查询服务</t>
+          <t>互联网上网服务营业场所经营监督检查信息分页查询服务</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>取水许可审批信息分页查询服务</t>
+          <t>互联网上网服务营业场所经营监督检查信息分页查询服务</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6213,9 +5889,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>True</t>
@@ -6227,17 +5901,15 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>6110</v>
+        <v>1247</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b1c70df090b64ef59c42de4894f4adb0/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f34e5919e6b84c1e9d3c62175b7243d0/detail</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -6250,17 +5922,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>畜牧业项目专家库人员名单信息数据量查询服务</t>
+          <t>招聘会信息数据量查询服务</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>公共安全</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>畜牧业项目专家库人员名单信息数据量查询服务</t>
+          <t>招聘会信息数据量查询服务</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6270,7 +5942,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6280,12 +5952,10 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>True</t>
@@ -6297,17 +5967,15 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>5900</v>
+        <v>199</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/86342dc141804c8b9655f89e5b7bb3d9/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f4bacf41196146bf8f297bf85a933fc6/detail</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -6320,17 +5988,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>劳务派遣机构资格行政许可信息数据量查询服务</t>
+          <t>淄川区日间照料中心名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>劳务派遣机构资格行政许可信息数据量查询服务</t>
+          <t>淄川区日间照料中心名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6353,9 +6021,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>True</t>
@@ -6367,17 +6033,15 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>5117</v>
+        <v>658</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9888da8905f4442792681c9ff90f4fec/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f94292f8335e47b28852451b95d52f3e/detail</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
@@ -6423,9 +6087,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>True</t>
@@ -6437,14 +6099,12 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>24814</v>
+        <v>25062</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/fde1c31591174f39aa5c7c11a4aaf9f8/detail</t>
@@ -6493,9 +6153,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>True</t>
@@ -6507,14 +6165,12 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ff67fcb2e95648ce9dd58f57882b96db/detail</t>
@@ -6530,17 +6186,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>律师执业信息数据量查询服务</t>
+          <t>危险化学品企业安全评价报告备案信息分页查询服务</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>律师执业信息数据量查询服务</t>
+          <t>危险化学品企业安全评价报告备案信息分页查询服务</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6550,7 +6206,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6563,9 +6219,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>True</t>
@@ -6577,17 +6231,15 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1362</v>
+        <v>20</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/00422fae4c684517b4654b00280c1759/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2f219f2e6e6a4ae7927782224de64892/detail</t>
         </is>
       </c>
       <c r="P88" t="inlineStr"/>
@@ -6600,7 +6252,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>淄川区日间照料中心名单信息分页查询服务</t>
+          <t>淄川区淄川工匠评选信息分页查询服务</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6610,7 +6262,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>淄川区日间照料中心名单信息分页查询服务</t>
+          <t>淄川区淄川工匠评选信息分页查询服务</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6620,7 +6272,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6633,9 +6285,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>True</t>
@@ -6647,17 +6297,15 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>668</v>
+        <v>17</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/041eed7ed0d84908a5370bf0a1acd41f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/309f284a35b243518a0ef289f3d4d037/detail</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -6670,27 +6318,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>星级酒店信息数据量查询服务</t>
+          <t>能源发展建设状况的信息分页查询服务</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>星级酒店信息数据量查询服务</t>
+          <t>能源发展建设状况的信息分页查询服务</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市临淄区</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6703,9 +6351,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>True</t>
@@ -6717,17 +6363,15 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1063</v>
+        <v>90</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/16aa3af31e024aac82f62dc58cfcf9a0/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3dcd8cfb1c984c5a9d2ff4ff91f5d0d3/detail</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
@@ -6740,17 +6384,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>安全生产检查信息数据量查询服务</t>
+          <t>淄川区齐鲁股权交易中心挂牌公司名录分页查询服务</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>财税金融</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>安全生产检查信息数据量查询服务</t>
+          <t>淄川区齐鲁股权交易中心挂牌公司名录分页查询服务</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6760,7 +6404,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6770,12 +6414,10 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>True</t>
@@ -6787,17 +6429,15 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7a7ea172d21c400d8b343985606a2a21/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/4a99e2e0f67f4579b1dbe9fa71b6ba6f/detail</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -6810,27 +6450,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>查处网吧及互联网上网服务信息数据量查询服务</t>
+          <t>畜禽生产统计信息数据量查询服务</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>查处网吧及互联网上网服务信息数据量查询服务</t>
+          <t>畜禽生产统计信息数据量查询服务</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>淄博市张店区</t>
+          <t>淄博市临淄区</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-11-26</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6840,12 +6480,10 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>True</t>
@@ -6857,17 +6495,15 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>172</v>
+        <v>49</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7ed3446d73c642088c44ae64259a9752/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/4b45289ec1a2496788479527b21d4591/detail</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -6880,27 +6516,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>淄川区齐鲁股权交易中心挂牌公司名录数据量查询服务</t>
+          <t>全县农村公路信息数据量查询服务</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>财税金融</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>淄川区齐鲁股权交易中心挂牌公司名录数据量查询服务</t>
+          <t>全县农村公路信息数据量查询服务</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市沂源县</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6910,12 +6546,10 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>True</t>
@@ -6927,17 +6561,15 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7f5a307d087f45a389541916da2fbf91/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/4d415994916548f1aa350172aff877d8/detail</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -6950,17 +6582,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>户外广告设置许可信息分页查询服务</t>
+          <t>安全生产检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>户外广告设置许可信息分页查询服务</t>
+          <t>安全生产检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6970,7 +6602,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6980,12 +6612,10 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>True</t>
@@ -6997,17 +6627,15 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2353</v>
+        <v>174</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8ae8238cad254507958f2cd5fe131b95/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7a7ea172d21c400d8b343985606a2a21/detail</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
@@ -7020,27 +6648,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>人民调解员信息分页查询服务</t>
+          <t>查处网吧及互联网上网服务信息数据量查询服务</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>人民调解员信息分页查询服务</t>
+          <t>查处网吧及互联网上网服务信息数据量查询服务</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市张店区</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7053,9 +6681,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>True</t>
@@ -7067,17 +6693,15 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cf87aae346924a2d9d9c1dbd95605cd7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7ed3446d73c642088c44ae64259a9752/detail</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -7090,17 +6714,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>烟花爆竹经营（零售）许可证核发信息分页查询服务</t>
+          <t>淄川区齐鲁股权交易中心挂牌公司名录数据量查询服务</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>财税金融</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>烟花爆竹经营（零售）许可证核发信息分页查询服务</t>
+          <t>淄川区齐鲁股权交易中心挂牌公司名录数据量查询服务</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7110,7 +6734,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7120,12 +6744,10 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>True</t>
@@ -7137,17 +6759,15 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>653</v>
+        <v>92</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d5f49212cd9249d2a88a06ab5874cb65/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7f5a307d087f45a389541916da2fbf91/detail</t>
         </is>
       </c>
       <c r="P96" t="inlineStr"/>
@@ -7160,27 +6780,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息分页查询服务</t>
+          <t>户外广告设置许可信息分页查询服务</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息分页查询服务</t>
+          <t>户外广告设置许可信息分页查询服务</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>淄博市桓台县</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7193,9 +6813,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>True</t>
@@ -7207,17 +6825,15 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2902</v>
+        <v>2360</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d9f872a9c21b406cb62cc28e96659f99/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/8ae8238cad254507958f2cd5fe131b95/detail</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -7230,27 +6846,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>危险化学品企业重大危险源备案信息分页查询服务</t>
+          <t>查处网吧及互联网上网服务信息分页查询服务</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>危险化学品企业重大危险源备案信息分页查询服务</t>
+          <t>查处网吧及互联网上网服务信息分页查询服务</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市张店区</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7263,9 +6879,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>True</t>
@@ -7277,17 +6891,15 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e092bea247bf4be0b2dcad084af62982/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/964b2f49d75a46b9af0fdd139469c2e4/detail</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
@@ -7300,17 +6912,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>畜牧业项目专家库人员名单信息分页查询服务</t>
+          <t>公证机构单位信息分页查询服务</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>畜牧业项目专家库人员名单信息分页查询服务</t>
+          <t>公证机构单位信息分页查询服务</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7320,7 +6932,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7333,9 +6945,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>True</t>
@@ -7347,17 +6957,15 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1458</v>
+        <v>213</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ed1d9fbc9f6140c9ab3b2d915786c23d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a45c944868c6425494e0e9bfeb3946af/detail</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -7370,17 +6978,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>蛋鸡规模养殖场基本信息数据量查询服务</t>
+          <t>星级酒店信息数据量查询服务</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>蛋鸡规模养殖场基本信息数据量查询服务</t>
+          <t>星级酒店信息数据量查询服务</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7390,7 +6998,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7403,9 +7011,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>True</t>
@@ -7417,17 +7023,15 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>268</v>
+        <v>1067</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f83e02cbfe7b4ddca40210531929332f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/16aa3af31e024aac82f62dc58cfcf9a0/detail</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -7440,27 +7044,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>律师事务所及分所信息数据量查询服务</t>
+          <t>能源发展建设状况的信息数据量查询服务</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>律师事务所及分所信息数据量查询服务</t>
+          <t>能源发展建设状况的信息数据量查询服务</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市临淄区</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7473,9 +7077,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>True</t>
@@ -7487,17 +7089,15 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>796</v>
+        <v>114</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/fa65eb3ce18e4912a6a84fa657d380bb/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1aa98854dcac491cacc428fd5f4a7f29/detail</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -7510,7 +7110,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>公证机构单位信息分页查询服务</t>
+          <t>律师执业信息分页查询服务</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7520,7 +7120,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>公证机构单位信息分页查询服务</t>
+          <t>律师执业信息分页查询服务</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7530,7 +7130,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7543,9 +7143,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>True</t>
@@ -7557,17 +7155,15 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>207</v>
+        <v>1380</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a45c944868c6425494e0e9bfeb3946af/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/238466219d6b4029a777056db3f685c2/detail</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7580,17 +7176,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>户外广告设置许可信息分页查询服务</t>
+          <t>淄川区农村幸福院名单信息分页查询服务</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>户外广告设置许可信息分页查询服务</t>
+          <t>淄川区农村幸福院名单信息分页查询服务</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7600,7 +7196,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7610,12 +7206,10 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>True</t>
@@ -7627,17 +7221,15 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2353</v>
+        <v>146</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8ae8238cad254507958f2cd5fe131b95/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/24a65bea73b54d2495a049a4458045dd/detail</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -7650,27 +7242,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>查处网吧及互联网上网服务信息分页查询服务</t>
+          <t>危险化学品企业重大危险源备案信息分页查询服务</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>查处网吧及互联网上网服务信息分页查询服务</t>
+          <t>危险化学品企业重大危险源备案信息分页查询服务</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>淄博市张店区</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7683,9 +7275,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>True</t>
@@ -7697,17 +7287,15 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/964b2f49d75a46b9af0fdd139469c2e4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e092bea247bf4be0b2dcad084af62982/detail</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -7720,17 +7308,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>律师执业信息数据量查询服务</t>
+          <t>畜牧业项目专家库人员名单信息分页查询服务</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>律师执业信息数据量查询服务</t>
+          <t>畜牧业项目专家库人员名单信息分页查询服务</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7753,9 +7341,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>True</t>
@@ -7767,17 +7353,15 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1362</v>
+        <v>1466</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
       </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/00422fae4c684517b4654b00280c1759/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ed1d9fbc9f6140c9ab3b2d915786c23d/detail</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -7790,17 +7374,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>淄川区日间照料中心名单信息分页查询服务</t>
+          <t>蛋鸡规模养殖场基本信息数据量查询服务</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>淄川区日间照料中心名单信息分页查询服务</t>
+          <t>蛋鸡规模养殖场基本信息数据量查询服务</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7823,9 +7407,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>True</t>
@@ -7837,17 +7419,15 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>668</v>
+        <v>278</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
       </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/041eed7ed0d84908a5370bf0a1acd41f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f83e02cbfe7b4ddca40210531929332f/detail</t>
         </is>
       </c>
       <c r="P106" t="inlineStr"/>
@@ -7860,17 +7440,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>烟花爆竹经营（零售）许可证核发信息分页查询服务</t>
+          <t>律师事务所及分所信息数据量查询服务</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>烟花爆竹经营（零售）许可证核发信息分页查询服务</t>
+          <t>律师事务所及分所信息数据量查询服务</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7880,7 +7460,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7893,9 +7473,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>True</t>
@@ -7907,17 +7485,15 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>653</v>
+        <v>805</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
       </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d5f49212cd9249d2a88a06ab5874cb65/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/fa65eb3ce18e4912a6a84fa657d380bb/detail</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
@@ -7930,22 +7506,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息分页查询服务</t>
+          <t>律师执业信息数据量查询服务</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息分页查询服务</t>
+          <t>律师执业信息数据量查询服务</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>淄博市桓台县</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7960,12 +7536,10 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>True</t>
@@ -7977,17 +7551,15 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2902</v>
+        <v>1373</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
       </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d9f872a9c21b406cb62cc28e96659f99/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/00422fae4c684517b4654b00280c1759/detail</t>
         </is>
       </c>
       <c r="P108" t="inlineStr"/>
@@ -8000,17 +7572,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>危险化学品企业重大危险源备案信息分页查询服务</t>
+          <t>淄川区日间照料中心名单信息分页查询服务</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>危险化学品企业重大危险源备案信息分页查询服务</t>
+          <t>淄川区日间照料中心名单信息分页查询服务</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8033,9 +7605,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>True</t>
@@ -8047,17 +7617,15 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>111</v>
+        <v>675</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
       </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e092bea247bf4be0b2dcad084af62982/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/041eed7ed0d84908a5370bf0a1acd41f/detail</t>
         </is>
       </c>
       <c r="P109" t="inlineStr"/>
@@ -8070,17 +7638,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>畜牧业项目专家库人员名单信息分页查询服务</t>
+          <t>人民调解员信息分页查询服务</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>畜牧业项目专家库人员名单信息分页查询服务</t>
+          <t>人民调解员信息分页查询服务</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8103,9 +7671,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>True</t>
@@ -8117,17 +7683,15 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1458</v>
+        <v>341</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
-      <c r="N110" t="n">
-        <v>0</v>
-      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ed1d9fbc9f6140c9ab3b2d915786c23d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cf87aae346924a2d9d9c1dbd95605cd7/detail</t>
         </is>
       </c>
       <c r="P110" t="inlineStr"/>
@@ -8140,17 +7704,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>蛋鸡规模养殖场基本信息数据量查询服务</t>
+          <t>烟花爆竹经营（零售）许可证核发信息分页查询服务</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>蛋鸡规模养殖场基本信息数据量查询服务</t>
+          <t>烟花爆竹经营（零售）许可证核发信息分页查询服务</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8160,7 +7724,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8173,9 +7737,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>True</t>
@@ -8187,17 +7749,15 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>268</v>
+        <v>660</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
       </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f83e02cbfe7b4ddca40210531929332f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d5f49212cd9249d2a88a06ab5874cb65/detail</t>
         </is>
       </c>
       <c r="P111" t="inlineStr"/>
@@ -8210,27 +7770,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>律师事务所及分所信息数据量查询服务</t>
+          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息分页查询服务</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>律师事务所及分所信息数据量查询服务</t>
+          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息分页查询服务</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市桓台县</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8240,12 +7800,10 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>True</t>
@@ -8257,17 +7815,15 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>796</v>
+        <v>2912</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
       </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/fa65eb3ce18e4912a6a84fa657d380bb/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d9f872a9c21b406cb62cc28e96659f99/detail</t>
         </is>
       </c>
       <c r="P112" t="inlineStr"/>
@@ -8280,27 +7836,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>娱乐场所经营监督检查数据量查询服务</t>
+          <t>作业场所职业病危害申报信息数据量查询服务</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>娱乐场所经营监督检查数据量查询服务</t>
+          <t>作业场所职业病危害申报信息数据量查询服务</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>淄博市张店区</t>
+          <t>淄博市高青县</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-21</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8313,9 +7869,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>True</t>
@@ -8327,17 +7881,15 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/12cd5f763ef84005b9a957828b04b22d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/03ec38dff5474449ad52b0fe9e821ff3/detail</t>
         </is>
       </c>
       <c r="P113" t="inlineStr"/>
@@ -8350,17 +7902,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>淄川区金牌工匠评选信息分页查询服务</t>
+          <t>道路运输车辆逾期未参加年度审验处罚信息分页查询服务</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>淄川区金牌工匠评选信息分页查询服务</t>
+          <t>道路运输车辆逾期未参加年度审验处罚信息分页查询服务</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8370,7 +7922,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8383,9 +7935,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>True</t>
@@ -8397,17 +7947,15 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>145</v>
+        <v>23001</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/154e4075893e4ed1ac0b8b02b2acfd83/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/04447540a3384986a1d440e3ccc5c511/detail</t>
         </is>
       </c>
       <c r="P114" t="inlineStr"/>
@@ -8420,27 +7968,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>全县农村公路信息分页查询服务</t>
+          <t>娱乐场所经营监督检查数据量查询服务</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>全县农村公路信息分页查询服务</t>
+          <t>娱乐场所经营监督检查数据量查询服务</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>淄博市沂源县</t>
+          <t>淄博市张店区</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8453,9 +8001,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>True</t>
@@ -8467,17 +8013,15 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
       </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1630b46bd4c744cba7803a896ac86ff7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/12cd5f763ef84005b9a957828b04b22d/detail</t>
         </is>
       </c>
       <c r="P115" t="inlineStr"/>
@@ -8490,27 +8034,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>作业场所职业病危害申报信息数据量查询服务</t>
+          <t>淄川区金牌工匠评选信息分页查询服务</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>作业场所职业病危害申报信息数据量查询服务</t>
+          <t>淄川区金牌工匠评选信息分页查询服务</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>淄博市高青县</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2018-12-21</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8523,9 +8067,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>True</t>
@@ -8537,17 +8079,15 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/03ec38dff5474449ad52b0fe9e821ff3/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/154e4075893e4ed1ac0b8b02b2acfd83/detail</t>
         </is>
       </c>
       <c r="P116" t="inlineStr"/>
@@ -8560,7 +8100,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>道路运输车辆逾期未参加年度审验处罚信息分页查询服务</t>
+          <t>全县农村公路信息分页查询服务</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8570,17 +8110,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>道路运输车辆逾期未参加年度审验处罚信息分页查询服务</t>
+          <t>全县农村公路信息分页查询服务</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市沂源县</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8593,9 +8133,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>True</t>
@@ -8607,17 +8145,15 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>22750</v>
+        <v>124</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/04447540a3384986a1d440e3ccc5c511/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1630b46bd4c744cba7803a896ac86ff7/detail</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
@@ -8630,22 +8166,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息数据量查询服务</t>
+          <t>基层法律服务工作者信息分页查询服务</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息数据量查询服务</t>
+          <t>基层法律服务工作者信息分页查询服务</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>淄博市桓台县</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8660,12 +8196,10 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>True</t>
@@ -8677,17 +8211,15 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2844</v>
+        <v>814</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
       </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cfc9692d4c644c268ac832e69cdeb42c/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2d0d330ddf5a42b294599894a83346e9/detail</t>
         </is>
       </c>
       <c r="P118" t="inlineStr"/>
@@ -8700,27 +8232,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>义教教研信息数据量查询服务</t>
+          <t>制定和调整相关财政补贴政策信息数据量查询服务</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>义教教研信息数据量查询服务</t>
+          <t>制定和调整相关财政补贴政策信息数据量查询服务</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>淄博市高青县</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2018-12-21</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8730,12 +8262,10 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>True</t>
@@ -8747,17 +8277,15 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>922</v>
+        <v>264</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
       </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5ca0c5ee464944678131285676c009b8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/364c92ba09ba48928c03102c8a8f02d8/detail</t>
         </is>
       </c>
       <c r="P119" t="inlineStr"/>
@@ -8770,17 +8298,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>山东省富民兴鲁劳动奖章推荐信息数据量查询服务</t>
+          <t>环卫基础设施信息数据量查询服务</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>山东省富民兴鲁劳动奖章推荐信息数据量查询服务</t>
+          <t>环卫基础设施信息数据量查询服务</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8790,7 +8318,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8803,9 +8331,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>True</t>
@@ -8817,17 +8343,15 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>180</v>
+        <v>1581</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
       </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5fdcec2d906546b5a47dab7be5f98022/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3b4f44345823454c873a43c7c43950ce/detail</t>
         </is>
       </c>
       <c r="P120" t="inlineStr"/>
@@ -8840,27 +8364,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>全国五一劳动奖状推荐信息数据量查询服务</t>
+          <t>作业场所职业病危害申报信息分页查询服务</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>全国五一劳动奖状推荐信息数据量查询服务</t>
+          <t>作业场所职业病危害申报信息分页查询服务</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市高青县</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-21</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8873,9 +8397,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>True</t>
@@ -8887,17 +8409,15 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
       </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/6a7674aac8c2466a82c82c8273c05403/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/4244781bf4384b38920648ac91015469/detail</t>
         </is>
       </c>
       <c r="P121" t="inlineStr"/>
@@ -8910,17 +8430,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>取水许可审批信息数据量查询服务</t>
+          <t>互联网上网服务营业场所经营监督检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>取水许可审批信息数据量查询服务</t>
+          <t>互联网上网服务营业场所经营监督检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8943,9 +8463,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>True</t>
@@ -8957,17 +8475,15 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>219</v>
+        <v>1116</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
       </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/737e7e0cae9c4dc6a797f0b3054ade7e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/473f309be11541a999a117f72388e9e6/detail</t>
         </is>
       </c>
       <c r="P122" t="inlineStr"/>
@@ -8980,27 +8496,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>招聘会信息分页查询服务</t>
+          <t>科技奖励信息数据量查询服务</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>公共安全</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>招聘会信息分页查询服务</t>
+          <t>科技奖励信息数据量查询服务</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市沂源县</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9013,9 +8529,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>True</t>
@@ -9027,17 +8541,15 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>155</v>
+        <v>43</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7883e24559534c45ada24ce619c394a6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/505c97604f5141b0bed1fca6102c09be/detail</t>
         </is>
       </c>
       <c r="P123" t="inlineStr"/>
@@ -9050,17 +8562,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>旅行社信息分页查询服务</t>
+          <t>基层法律服务工作者信息数据量查询服务</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>旅行社信息分页查询服务</t>
+          <t>基层法律服务工作者信息数据量查询服务</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9070,7 +8582,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9083,9 +8595,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>True</t>
@@ -9097,17 +8607,15 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2518</v>
+        <v>1279</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
       </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/78d879e34bcb4f68bb68db1b4a108828/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/55c1c00177d547e5b1cdd5828b540721/detail</t>
         </is>
       </c>
       <c r="P124" t="inlineStr"/>
@@ -9120,27 +8628,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>在公路上检查道路运输车辆信息分页查询服务</t>
+          <t>义教教研信息数据量查询服务</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>在公路上检查道路运输车辆信息分页查询服务</t>
+          <t>义教教研信息数据量查询服务</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市高青县</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2018-12-21</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9150,12 +8658,10 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>True</t>
@@ -9167,17 +8673,15 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>28226</v>
+        <v>928</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
       </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7b1425901e3c49f5a5d74787e700d139/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5ca0c5ee464944678131285676c009b8/detail</t>
         </is>
       </c>
       <c r="P125" t="inlineStr"/>
@@ -9190,17 +8694,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>基层法律服务工作者信息分页查询服务</t>
+          <t>山东省富民兴鲁劳动奖章推荐信息数据量查询服务</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>基层法律服务工作者信息分页查询服务</t>
+          <t>山东省富民兴鲁劳动奖章推荐信息数据量查询服务</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9210,7 +8714,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9223,9 +8727,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>True</t>
@@ -9237,17 +8739,15 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>809</v>
+        <v>187</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
       </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2d0d330ddf5a42b294599894a83346e9/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5fdcec2d906546b5a47dab7be5f98022/detail</t>
         </is>
       </c>
       <c r="P126" t="inlineStr"/>
@@ -9260,17 +8760,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>制定和调整相关财政补贴政策信息数据量查询服务</t>
+          <t>全国五一劳动奖状推荐信息数据量查询服务</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>制定和调整相关财政补贴政策信息数据量查询服务</t>
+          <t>全国五一劳动奖状推荐信息数据量查询服务</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9280,7 +8780,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9293,9 +8793,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>True</t>
@@ -9307,17 +8805,15 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>250</v>
+        <v>142</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
       </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/364c92ba09ba48928c03102c8a8f02d8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/6a7674aac8c2466a82c82c8273c05403/detail</t>
         </is>
       </c>
       <c r="P127" t="inlineStr"/>
@@ -9330,17 +8826,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>环卫基础设施信息数据量查询服务</t>
+          <t>取水许可审批信息数据量查询服务</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>环卫基础设施信息数据量查询服务</t>
+          <t>取水许可审批信息数据量查询服务</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -9350,7 +8846,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9363,9 +8859,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>True</t>
@@ -9377,17 +8871,15 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1571</v>
+        <v>226</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
       </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3b4f44345823454c873a43c7c43950ce/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/737e7e0cae9c4dc6a797f0b3054ade7e/detail</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -9400,27 +8892,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>作业场所职业病危害申报信息分页查询服务</t>
+          <t>招聘会信息分页查询服务</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>公共安全</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>作业场所职业病危害申报信息分页查询服务</t>
+          <t>招聘会信息分页查询服务</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>淄博市高青县</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2018-12-21</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9430,12 +8922,10 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>True</t>
@@ -9447,17 +8937,15 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
       </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/4244781bf4384b38920648ac91015469/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7883e24559534c45ada24ce619c394a6/detail</t>
         </is>
       </c>
       <c r="P129" t="inlineStr"/>
@@ -9470,7 +8958,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>互联网上网服务营业场所经营监督检查信息数据量查询服务</t>
+          <t>旅行社信息分页查询服务</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9480,7 +8968,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>互联网上网服务营业场所经营监督检查信息数据量查询服务</t>
+          <t>旅行社信息分页查询服务</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9490,7 +8978,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9503,9 +8991,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>True</t>
@@ -9517,17 +9003,15 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1111</v>
+        <v>2524</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
       </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/473f309be11541a999a117f72388e9e6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/78d879e34bcb4f68bb68db1b4a108828/detail</t>
         </is>
       </c>
       <c r="P130" t="inlineStr"/>
@@ -9540,17 +9024,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>淄川区各级畜禽养殖示范场名单信息数据量查询服务</t>
+          <t>在公路上检查道路运输车辆信息分页查询服务</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>淄川区各级畜禽养殖示范场名单信息数据量查询服务</t>
+          <t>在公路上检查道路运输车辆信息分页查询服务</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9573,9 +9057,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>True</t>
@@ -9587,17 +9069,15 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>169</v>
+        <v>28474</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
       </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b5dde7a714b9418d9b30a43f87741760/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7b1425901e3c49f5a5d74787e700d139/detail</t>
         </is>
       </c>
       <c r="P131" t="inlineStr"/>
@@ -9610,17 +9090,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>货运经营者没有采取货物脱落扬撒处罚信息分页查询服务</t>
+          <t>劳务派遣机构资格行政许可信息分页查询服务</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>货运经营者没有采取货物脱落扬撒处罚信息分页查询服务</t>
+          <t>劳务派遣机构资格行政许可信息分页查询服务</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9643,9 +9123,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>True</t>
@@ -9657,17 +9135,15 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1428</v>
+        <v>175</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
       </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9365133fadca4a4fae5bbdb7a20a8daf/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7cbfd9ae8a234aaca5a0522b2bde0b31/detail</t>
         </is>
       </c>
       <c r="P132" t="inlineStr"/>
@@ -9680,17 +9156,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>基层法律服务工作者信息数据量查询服务</t>
+          <t>淄川区淄川工匠评选信息数据量查询服务</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>基层法律服务工作者信息数据量查询服务</t>
+          <t>淄川区淄川工匠评选信息数据量查询服务</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9700,7 +9176,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9713,9 +9189,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>True</t>
@@ -9727,17 +9201,15 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1273</v>
+        <v>17</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/55c1c00177d547e5b1cdd5828b540721/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/800e3b109ffc42b9b5bdce1118d3779a/detail</t>
         </is>
       </c>
       <c r="P133" t="inlineStr"/>
@@ -9750,27 +9222,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>义教教研信息数据量查询服务</t>
+          <t>在公路上检查道路运输车辆信息数据量查询服务</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>义教教研信息数据量查询服务</t>
+          <t>在公路上检查道路运输车辆信息数据量查询服务</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>淄博市高青县</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2018-12-21</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -9780,12 +9252,10 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>True</t>
@@ -9797,17 +9267,15 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>922</v>
+        <v>28617</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
       </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5ca0c5ee464944678131285676c009b8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9099a91a38a44353bb3eebb3c1becc36/detail</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -9820,17 +9288,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>山东省富民兴鲁劳动奖章推荐信息数据量查询服务</t>
+          <t>货运经营者没有采取货物脱落扬撒处罚信息分页查询服务</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>山东省富民兴鲁劳动奖章推荐信息数据量查询服务</t>
+          <t>货运经营者没有采取货物脱落扬撒处罚信息分页查询服务</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9840,7 +9308,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -9853,9 +9321,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>True</t>
@@ -9867,17 +9333,15 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>180</v>
+        <v>1435</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
       </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5fdcec2d906546b5a47dab7be5f98022/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9365133fadca4a4fae5bbdb7a20a8daf/detail</t>
         </is>
       </c>
       <c r="P135" t="inlineStr"/>
@@ -9890,17 +9354,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>作业场所职业病危害申报信息数据量查询服务</t>
+          <t>义教教研信息分页查询服务</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>作业场所职业病危害申报信息数据量查询服务</t>
+          <t>义教教研信息分页查询服务</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9920,12 +9384,10 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>True</t>
@@ -9937,17 +9399,15 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>192</v>
+        <v>917</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
       </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/03ec38dff5474449ad52b0fe9e821ff3/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9ba4eaadbd4748eca3d5a27575d65c22/detail</t>
         </is>
       </c>
       <c r="P136" t="inlineStr"/>
@@ -9960,27 +9420,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>道路运输车辆逾期未参加年度审验处罚信息分页查询服务</t>
+          <t>娱乐场所经营监督检查分页查询服务</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>道路运输车辆逾期未参加年度审验处罚信息分页查询服务</t>
+          <t>娱乐场所经营监督检查分页查询服务</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>淄博市淄川区</t>
+          <t>淄博市张店区</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9993,9 +9453,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>True</t>
@@ -10007,17 +9465,15 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>22750</v>
+        <v>244</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
       </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/04447540a3384986a1d440e3ccc5c511/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a4963d38f21345fca8065207bc9b55f9/detail</t>
         </is>
       </c>
       <c r="P137" t="inlineStr"/>
@@ -10030,27 +9486,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>娱乐场所经营监督检查数据量查询服务</t>
+          <t>淄川区各级畜禽养殖示范场名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>娱乐场所经营监督检查数据量查询服务</t>
+          <t>淄川区各级畜禽养殖示范场名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>淄博市张店区</t>
+          <t>淄博市淄川区</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10063,9 +9519,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>True</t>
@@ -10077,17 +9531,15 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
       </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/12cd5f763ef84005b9a957828b04b22d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b5dde7a714b9418d9b30a43f87741760/detail</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
@@ -10100,17 +9552,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>淄川区金牌工匠评选信息分页查询服务</t>
+          <t>职业卫生检查信息分页查询服务</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>淄川区金牌工匠评选信息分页查询服务</t>
+          <t>职业卫生检查信息分页查询服务</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -10120,7 +9572,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10133,9 +9585,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>True</t>
@@ -10147,17 +9597,15 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
       </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/154e4075893e4ed1ac0b8b02b2acfd83/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c92cbc43fe1e4855b15d95ed6f2786d9/detail</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -10170,27 +9618,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>全县农村公路信息分页查询服务</t>
+          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息数据量查询服务</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>全县农村公路信息分页查询服务</t>
+          <t>桓台县中职学校县级三好学生、优秀学生干部评选表彰信息数据量查询服务</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>淄博市沂源县</t>
+          <t>淄博市桓台县</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10200,12 +9648,10 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>True</t>
@@ -10217,17 +9663,15 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>119</v>
+        <v>2856</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
       </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1630b46bd4c744cba7803a896ac86ff7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cfc9692d4c644c268ac832e69cdeb42c/detail</t>
         </is>
       </c>
       <c r="P140" t="inlineStr"/>
@@ -10240,17 +9684,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>基层法律服务工作者信息分页查询服务</t>
+          <t>生猪经营资格备案登记信息数据量查询服务</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>基层法律服务工作者信息分页查询服务</t>
+          <t>生猪经营资格备案登记信息数据量查询服务</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -10260,7 +9704,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2018-12-20</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10273,9 +9717,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>True</t>
@@ -10287,17 +9729,15 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>809</v>
+        <v>1437</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
       </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2d0d330ddf5a42b294599894a83346e9/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f8064cfb171c446abf4c5379f56f3dd7/detail</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -10310,22 +9750,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>受监工程的交工、竣工验收前的质量检测及质量等级的初定信息分页查询服务</t>
+          <t>医疗保险定点医院单位信息分页查询服务</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>受监工程的交工、竣工验收前的质量检测及质量等级的初定信息分页查询服务</t>
+          <t>医疗保险定点医院单位信息分页查询服务</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>淄博市交通运输局</t>
+          <t>淄博市人力资源和社会保障局</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -10343,9 +9783,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>True</t>
@@ -10357,17 +9795,15 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>74</v>
+        <v>5535</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
       </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1c82aae9fcff44ac83df677ca6d14d00/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/039d254eada24c69bde63670fb19e19e/detail</t>
         </is>
       </c>
       <c r="P142" t="inlineStr"/>
@@ -10380,7 +9816,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>公路水运工程的质量监督信息数据量查询服务</t>
+          <t>受监工程的交工、竣工验收前的质量检测及质量等级的初定信息分页查询服务</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10390,7 +9826,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>公路水运工程的质量监督信息数据量查询服务</t>
+          <t>受监工程的交工、竣工验收前的质量检测及质量等级的初定信息分页查询服务</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10413,9 +9849,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>True</t>
@@ -10427,17 +9861,15 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
       </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/22bdcdce9b604d0da9b27572962a5b1b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1c82aae9fcff44ac83df677ca6d14d00/detail</t>
         </is>
       </c>
       <c r="P143" t="inlineStr"/>
@@ -10450,23 +9882,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>对外劳务合作经营信息分页查询服务</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
+          <t>公路水运工程的质量监督信息数据量查询服务</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>交通出行</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>对外劳务合作经营信息分页查询服务</t>
+          <t>公路水运工程的质量监督信息数据量查询服务</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>淄博市商务局</t>
+          <t>淄博市交通运输局</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10479,9 +9915,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>True</t>
@@ -10493,17 +9927,15 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>363</v>
+        <v>207</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
       </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/297314f6de5c46a4b9ab981f956381e2/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/22bdcdce9b604d0da9b27572962a5b1b/detail</t>
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
@@ -10516,27 +9948,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>机动车登记服务站信息数据量查询服务</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>社保就业</t>
-        </is>
-      </c>
+          <t>对外劳务合作经营信息分页查询服务</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>机动车登记服务站信息数据量查询服务</t>
+          <t>对外劳务合作经营信息分页查询服务</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市商务局</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10549,9 +9977,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>True</t>
@@ -10563,17 +9989,15 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2517</v>
+        <v>564</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
       </c>
-      <c r="N145" t="n">
-        <v>0</v>
-      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/34b303cdd3714a2198ab4089d0a722d7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/297314f6de5c46a4b9ab981f956381e2/detail</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -10586,7 +10010,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>全市看守所、拘留所信息数据量查询服务</t>
+          <t>机动车登记服务站信息数据量查询服务</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10596,7 +10020,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>全市看守所、拘留所信息数据量查询服务</t>
+          <t>机动车登记服务站信息数据量查询服务</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10606,7 +10030,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10619,9 +10043,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>True</t>
@@ -10633,17 +10055,15 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>400</v>
+        <v>2523</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
       </c>
-      <c r="N146" t="n">
-        <v>0</v>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/37f5037d1f714076b4594ba702e68457/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/34b303cdd3714a2198ab4089d0a722d7/detail</t>
         </is>
       </c>
       <c r="P146" t="inlineStr"/>
@@ -10656,27 +10076,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>受监工程的交工、竣工验收前的质量检测及质量等级的初定信息数据量查询服务</t>
+          <t>全市看守所、拘留所信息数据量查询服务</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>受监工程的交工、竣工验收前的质量检测及质量等级的初定信息数据量查询服务</t>
+          <t>全市看守所、拘留所信息数据量查询服务</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>淄博市交通运输局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -10689,9 +10109,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>True</t>
@@ -10703,17 +10121,15 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>72</v>
+        <v>410</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
       </c>
-      <c r="N147" t="n">
-        <v>0</v>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3dea694c91cb49e98b34f41d571a4baa/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/37f5037d1f714076b4594ba702e68457/detail</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
@@ -10726,7 +10142,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>事故处理点信息分页查询服务</t>
+          <t>受监工程的交工、竣工验收前的质量检测及质量等级的初定信息数据量查询服务</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10736,17 +10152,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>事故处理点信息分页查询服务</t>
+          <t>受监工程的交工、竣工验收前的质量检测及质量等级的初定信息数据量查询服务</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市交通运输局</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -10759,9 +10175,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>True</t>
@@ -10773,17 +10187,15 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>309</v>
+        <v>74</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
       </c>
-      <c r="N148" t="n">
-        <v>0</v>
-      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/426aa3a87c58480293ddc1fead8188bc/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3dea694c91cb49e98b34f41d571a4baa/detail</t>
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
@@ -10796,17 +10208,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>全市刻章单位信息分页查询服务</t>
+          <t>事故处理点信息分页查询服务</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>全市刻章单位信息分页查询服务</t>
+          <t>事故处理点信息分页查询服务</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -10816,7 +10228,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -10829,9 +10241,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>True</t>
@@ -10843,17 +10253,15 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
       </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/54d9deb98bb849f8bf4178fd1e703403/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/426aa3a87c58480293ddc1fead8188bc/detail</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
@@ -10866,27 +10274,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>拟定全市博物馆事业发展规划信息数据量查询服务</t>
+          <t>全市刻章单位信息分页查询服务</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>拟定全市博物馆事业发展规划信息数据量查询服务</t>
+          <t>全市刻章单位信息分页查询服务</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>淄博市文化和旅游局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -10896,12 +10304,10 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>True</t>
@@ -10913,17 +10319,15 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1104</v>
+        <v>282</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
       </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5ccc2a36a1374efc9d3346d0fbf5e097/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/54d9deb98bb849f8bf4178fd1e703403/detail</t>
         </is>
       </c>
       <c r="P150" t="inlineStr"/>
@@ -10936,27 +10340,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>医疗保险定点医院单位信息分页查询服务</t>
+          <t>拟定全市博物馆事业发展规划信息数据量查询服务</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>医疗保险定点医院单位信息分页查询服务</t>
+          <t>拟定全市博物馆事业发展规划信息数据量查询服务</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>淄博市人力资源和社会保障局</t>
+          <t>淄博市文化和旅游局</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -10966,12 +10370,10 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>True</t>
@@ -10983,17 +10385,15 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>5330</v>
+        <v>1112</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
       </c>
-      <c r="N151" t="n">
-        <v>0</v>
-      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/039d254eada24c69bde63670fb19e19e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5ccc2a36a1374efc9d3346d0fbf5e097/detail</t>
         </is>
       </c>
       <c r="P151" t="inlineStr"/>
@@ -11006,17 +10406,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>执法机构统信息数据量查询服务</t>
+          <t>机动车检测站信息数据量查询服务</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>执法机构统信息数据量查询服务</t>
+          <t>机动车检测站信息数据量查询服务</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -11039,9 +10439,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>True</t>
@@ -11053,17 +10451,15 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>16405</v>
+        <v>1578</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
       </c>
-      <c r="N152" t="n">
-        <v>0</v>
-      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/961c3eb38929430ca8cb5d33f52a1bee/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/804b321f0942497797061cc0d05625be/detail</t>
         </is>
       </c>
       <c r="P152" t="inlineStr"/>
@@ -11076,17 +10472,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>典当场所信息分页查询服务</t>
+          <t>执法机构统信息数据量查询服务</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>典当场所信息分页查询服务</t>
+          <t>执法机构统信息数据量查询服务</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -11109,9 +10505,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>True</t>
@@ -11123,17 +10517,15 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>215</v>
+        <v>16855</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
       </c>
-      <c r="N153" t="n">
-        <v>0</v>
-      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d298dfef4a48445188e79455978ca8b4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/961c3eb38929430ca8cb5d33f52a1bee/detail</t>
         </is>
       </c>
       <c r="P153" t="inlineStr"/>
@@ -11146,22 +10538,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>重点实验室名单信息数据量查询服务</t>
+          <t>医疗保险定点门诊单位信息分页查询服务</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>重点实验室名单信息数据量查询服务</t>
+          <t>医疗保险定点门诊单位信息分页查询服务</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>淄博市科技局</t>
+          <t>淄博市人力资源和社会保障局</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11176,12 +10568,10 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>True</t>
@@ -11193,17 +10583,15 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1139</v>
+        <v>760</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
       </c>
-      <c r="N154" t="n">
-        <v>0</v>
-      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d8893239f4f84a5eac7b3a2f265eb475/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9b65e9fd174a4e60bd481fa1350be8e3/detail</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
@@ -11216,22 +10604,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>公路水运工程的质量监督信息分页查询服务</t>
+          <t>机动车检测站信息分页查询服务</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>公路水运工程的质量监督信息分页查询服务</t>
+          <t>机动车检测站信息分页查询服务</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>淄博市交通运输局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11249,9 +10637,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>True</t>
@@ -11263,17 +10649,15 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>184</v>
+        <v>1554</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
       </c>
-      <c r="N155" t="n">
-        <v>0</v>
-      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ac848f0b0fed4b43bca46a9e597a3e1f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a52a73e3892d472dbe13ddebbcaec84b/detail</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
@@ -11286,7 +10670,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>机动车登记服务站信息分页查询服务</t>
+          <t>医疗保险定点医院单位信息数据量查询服务</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11296,12 +10680,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>机动车登记服务站信息分页查询服务</t>
+          <t>医疗保险定点医院单位信息数据量查询服务</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市人力资源和社会保障局</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11319,9 +10703,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>True</t>
@@ -11333,17 +10715,15 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2525</v>
+        <v>5367</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
       </c>
-      <c r="N156" t="n">
-        <v>0</v>
-      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b43bcfc899ab45d3be044adc618beb7d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a722ac09e03643dd8180ad516a35a9de/detail</t>
         </is>
       </c>
       <c r="P156" t="inlineStr"/>
@@ -11356,22 +10736,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>典当场所信息数据量查询服务</t>
+          <t>公路水运工程的质量监督信息分页查询服务</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>典当场所信息数据量查询服务</t>
+          <t>公路水运工程的质量监督信息分页查询服务</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市交通运输局</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11389,9 +10769,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>True</t>
@@ -11403,17 +10781,15 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
       </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e7f8999dafa3420fa5678dd670dc6769/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ac848f0b0fed4b43bca46a9e597a3e1f/detail</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -11426,27 +10802,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>拟定全市博物馆事业发展规划信息数据量查询服务</t>
+          <t>机动车登记服务站信息分页查询服务</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>拟定全市博物馆事业发展规划信息数据量查询服务</t>
+          <t>机动车登记服务站信息分页查询服务</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>淄博市文化和旅游局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11456,12 +10832,10 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>True</t>
@@ -11473,17 +10847,15 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1104</v>
+        <v>2532</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
       </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5ccc2a36a1374efc9d3346d0fbf5e097/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b43bcfc899ab45d3be044adc618beb7d/detail</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
@@ -11496,27 +10868,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>医疗保险定点门诊单位信息分页查询服务</t>
+          <t>典当场所信息分页查询服务</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>医疗保险定点门诊单位信息分页查询服务</t>
+          <t>典当场所信息分页查询服务</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>淄博市人力资源和社会保障局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2018-11-26</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11529,9 +10901,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I159" t="n">
-        <v>0</v>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>True</t>
@@ -11543,17 +10913,15 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>556</v>
+        <v>217</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
       </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9b65e9fd174a4e60bd481fa1350be8e3/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d298dfef4a48445188e79455978ca8b4/detail</t>
         </is>
       </c>
       <c r="P159" t="inlineStr"/>
@@ -11566,27 +10934,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>机动车检测站信息分页查询服务</t>
+          <t>重点实验室名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>机动车检测站信息分页查询服务</t>
+          <t>重点实验室名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市科技局</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018-11-26</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11596,12 +10964,10 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>True</t>
@@ -11613,17 +10979,15 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1549</v>
+        <v>1337</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
       </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a52a73e3892d472dbe13ddebbcaec84b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d8893239f4f84a5eac7b3a2f265eb475/detail</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -11636,22 +11000,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>医疗保险定点医院单位信息数据量查询服务</t>
+          <t>典当场所信息数据量查询服务</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>医疗保险定点医院单位信息数据量查询服务</t>
+          <t>典当场所信息数据量查询服务</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>淄博市人力资源和社会保障局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -11669,9 +11033,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>True</t>
@@ -11683,17 +11045,15 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>5165</v>
+        <v>188</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
       </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a722ac09e03643dd8180ad516a35a9de/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e7f8999dafa3420fa5678dd670dc6769/detail</t>
         </is>
       </c>
       <c r="P161" t="inlineStr"/>
@@ -11706,22 +11066,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>中等职业学校名录数据量查询服务</t>
+          <t>派出所信息数据量查询服务</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>中等职业学校名录数据量查询服务</t>
+          <t>派出所信息数据量查询服务</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>淄博市教育局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -11736,12 +11096,10 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>True</t>
@@ -11753,17 +11111,15 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>228</v>
+        <v>4193</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
       </c>
-      <c r="N162" t="n">
-        <v>0</v>
-      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7c3fb439da3e447c8f1d352d43608683/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/09f95a2d52d64a35bb53735bd9e99788/detail</t>
         </is>
       </c>
       <c r="P162" t="inlineStr"/>
@@ -11776,17 +11132,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>旅馆信息分页查询服务</t>
+          <t>保安公司信息分页查询服务</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>旅馆信息分页查询服务</t>
+          <t>保安公司信息分页查询服务</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -11809,9 +11165,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>True</t>
@@ -11823,17 +11177,15 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>276</v>
+        <v>5110</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
-      </c>
-      <c r="N163" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7d82b9f5c84c4445a3fcf3436763f078/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3534af03285149e5b11d81c3f2c5f778/detail</t>
         </is>
       </c>
       <c r="P163" t="inlineStr"/>
@@ -11846,27 +11198,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>保安公司信息分页查询服务</t>
+          <t>美术品经营监督检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>保安公司信息分页查询服务</t>
+          <t>美术品经营监督检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市文化市场执法支队</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -11876,12 +11228,10 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>True</t>
@@ -11893,17 +11243,15 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>5099</v>
+        <v>58</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
       </c>
-      <c r="N164" t="n">
-        <v>0</v>
-      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3534af03285149e5b11d81c3f2c5f778/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/568c81d9f21540beb6d15521f2187da0/detail</t>
         </is>
       </c>
       <c r="P164" t="inlineStr"/>
@@ -11916,27 +11264,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>营业性演出监督检查信息分页查询服务</t>
+          <t>中等职业学校名录数据量查询服务</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>营业性演出监督检查信息分页查询服务</t>
+          <t>中等职业学校名录数据量查询服务</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>淄博市文化市场执法支队</t>
+          <t>淄博市教育局</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -11949,9 +11297,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>True</t>
@@ -11963,17 +11309,15 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
       </c>
-      <c r="N165" t="n">
-        <v>0</v>
-      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/bb335e41b0464a718c47e9de07e2f689/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7c3fb439da3e447c8f1d352d43608683/detail</t>
         </is>
       </c>
       <c r="P165" t="inlineStr"/>
@@ -11986,7 +11330,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>美术品经营监督检查信息分页查询服务</t>
+          <t>旅馆信息分页查询服务</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11996,17 +11340,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>美术品经营监督检查信息分页查询服务</t>
+          <t>旅馆信息分页查询服务</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>淄博市文化市场执法支队</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12016,12 +11360,10 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>True</t>
@@ -12033,17 +11375,15 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>44</v>
+        <v>286</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
-      </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/bdb99ba407314257a6460db151fb9f37/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7d82b9f5c84c4445a3fcf3436763f078/detail</t>
         </is>
       </c>
       <c r="P166" t="inlineStr"/>
@@ -12056,22 +11396,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>旅馆信息数据量查询服务</t>
+          <t>淄博市幼儿园信息分页查询服务</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>旅馆信息数据量查询服务</t>
+          <t>淄博市幼儿园信息分页查询服务</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市教育局</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -12086,12 +11426,10 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>True</t>
@@ -12103,17 +11441,15 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>302</v>
+        <v>24374</v>
       </c>
       <c r="M167" t="n">
         <v>1</v>
       </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ae12e6d21f74408094f4ec1c48fb0fdd/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/84bb3bbd0f0d419c97b551c553ea4781/detail</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -12126,22 +11462,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>淄博市幼儿园信息分页查询服务</t>
+          <t>驾驶考试场信息数据量查询服务</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>淄博市幼儿园信息分页查询服务</t>
+          <t>驾驶考试场信息数据量查询服务</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>淄博市教育局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -12156,12 +11492,10 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>True</t>
@@ -12173,17 +11507,15 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>24122</v>
+        <v>322</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/84bb3bbd0f0d419c97b551c553ea4781/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/8bdeeefc6cf149c2838d7cab1585bee2/detail</t>
         </is>
       </c>
       <c r="P168" t="inlineStr"/>
@@ -12196,7 +11528,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>驾驶考试场信息数据量查询服务</t>
+          <t>淄博市国家级酒店信息分页查询服务</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -12206,17 +11538,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>驾驶考试场信息数据量查询服务</t>
+          <t>淄博市国家级酒店信息分页查询服务</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市商务局</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12229,9 +11561,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>0</v>
-      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>True</t>
@@ -12243,17 +11573,15 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>299</v>
+        <v>203</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
-      </c>
-      <c r="N169" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8bdeeefc6cf149c2838d7cab1585bee2/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/972c18330b894fae8d546d1497406e40/detail</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -12266,27 +11594,27 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>淄博市国家级酒店信息分页查询服务</t>
+          <t>重点实验室名单信息分页查询服务</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>淄博市国家级酒店信息分页查询服务</t>
+          <t>重点实验室名单信息分页查询服务</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>淄博市商务局</t>
+          <t>淄博市科技局</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-11-26</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12296,12 +11624,10 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I170" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>True</t>
@@ -12313,17 +11639,15 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>196</v>
+        <v>1328</v>
       </c>
       <c r="M170" t="n">
-        <v>1</v>
-      </c>
-      <c r="N170" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/972c18330b894fae8d546d1497406e40/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/988019c539ba46f4899feb6d11e74777/detail</t>
         </is>
       </c>
       <c r="P170" t="inlineStr"/>
@@ -12336,27 +11660,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>重点实验室名单信息分页查询服务</t>
+          <t>终生禁驾名单信息分页查询服务</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>重点实验室名单信息分页查询服务</t>
+          <t>终生禁驾名单信息分页查询服务</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>淄博市科技局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2018-11-26</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12366,12 +11690,10 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>True</t>
@@ -12383,17 +11705,15 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1129</v>
+        <v>28769</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
       </c>
-      <c r="N171" t="n">
-        <v>0</v>
-      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/988019c539ba46f4899feb6d11e74777/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/989cadd0ecc0478f871c2bd277fb460b/detail</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -12406,17 +11726,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>事故处理点信息数据量查询服务</t>
+          <t>旅馆信息数据量查询服务</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>事故处理点信息数据量查询服务</t>
+          <t>旅馆信息数据量查询服务</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -12426,7 +11746,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12439,9 +11759,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>True</t>
@@ -12453,17 +11771,15 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
-      </c>
-      <c r="N172" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f95585be05834f0aa22792c23eba2d0e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ae12e6d21f74408094f4ec1c48fb0fdd/detail</t>
         </is>
       </c>
       <c r="P172" t="inlineStr"/>
@@ -12476,27 +11792,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>保安公司信息分页查询服务</t>
+          <t>营业性演出监督检查信息分页查询服务</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>保安公司信息分页查询服务</t>
+          <t>营业性演出监督检查信息分页查询服务</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市文化市场执法支队</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12506,12 +11822,10 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>True</t>
@@ -12523,17 +11837,15 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>5099</v>
+        <v>72</v>
       </c>
       <c r="M173" t="n">
         <v>0</v>
       </c>
-      <c r="N173" t="n">
-        <v>0</v>
-      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3534af03285149e5b11d81c3f2c5f778/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/bb335e41b0464a718c47e9de07e2f689/detail</t>
         </is>
       </c>
       <c r="P173" t="inlineStr"/>
@@ -12546,7 +11858,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>美术品经营监督检查信息数据量查询服务</t>
+          <t>美术品经营监督检查信息分页查询服务</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -12556,7 +11868,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>美术品经营监督检查信息数据量查询服务</t>
+          <t>美术品经营监督检查信息分页查询服务</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -12579,9 +11891,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>0</v>
-      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>True</t>
@@ -12593,17 +11903,15 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
       </c>
-      <c r="N174" t="n">
-        <v>0</v>
-      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/568c81d9f21540beb6d15521f2187da0/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/bdb99ba407314257a6460db151fb9f37/detail</t>
         </is>
       </c>
       <c r="P174" t="inlineStr"/>
@@ -12616,22 +11924,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>旅馆信息数据量查询服务</t>
+          <t>淄博市幼儿园信息数据量查询服务</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>旅馆信息数据量查询服务</t>
+          <t>淄博市幼儿园信息数据量查询服务</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市教育局</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -12646,12 +11954,10 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I175" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>True</t>
@@ -12663,17 +11969,15 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>302</v>
+        <v>30782</v>
       </c>
       <c r="M175" t="n">
-        <v>1</v>
-      </c>
-      <c r="N175" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ae12e6d21f74408094f4ec1c48fb0fdd/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e05e67564c524deeafe7886c54d9c078/detail</t>
         </is>
       </c>
       <c r="P175" t="inlineStr"/>
@@ -12686,27 +11990,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>营业性演出监督检查信息分页查询服务</t>
+          <t>中等职业学校名录分页查询服务</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>营业性演出监督检查信息分页查询服务</t>
+          <t>中等职业学校名录分页查询服务</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>淄博市文化市场执法支队</t>
+          <t>淄博市教育局</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -12719,9 +12023,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I176" t="n">
-        <v>0</v>
-      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>True</t>
@@ -12733,17 +12035,15 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>66</v>
+        <v>206</v>
       </c>
       <c r="M176" t="n">
         <v>0</v>
       </c>
-      <c r="N176" t="n">
-        <v>0</v>
-      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/bb335e41b0464a718c47e9de07e2f689/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e72cf4988ebb435985b9c28822222da6/detail</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -12756,17 +12056,13 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>淄博市国家级酒店信息分页查询服务</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>社会民生</t>
-        </is>
-      </c>
+          <t>对外劳务合作经营信息数据量查询服务</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>淄博市国家级酒店信息分页查询服务</t>
+          <t>对外劳务合作经营信息数据量查询服务</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -12789,9 +12085,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I177" t="n">
-        <v>0</v>
-      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>True</t>
@@ -12803,17 +12097,15 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>196</v>
+        <v>525</v>
       </c>
       <c r="M177" t="n">
-        <v>1</v>
-      </c>
-      <c r="N177" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/972c18330b894fae8d546d1497406e40/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ed07c4afdb6248238010865fef29ea5d/detail</t>
         </is>
       </c>
       <c r="P177" t="inlineStr"/>
@@ -12826,27 +12118,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>重点实验室名单信息分页查询服务</t>
+          <t>保安公司信息数据量查询服务</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>重点实验室名单信息分页查询服务</t>
+          <t>保安公司信息数据量查询服务</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>淄博市科技局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2018-11-26</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -12856,12 +12148,10 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I178" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>True</t>
@@ -12873,17 +12163,15 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1129</v>
+        <v>5106</v>
       </c>
       <c r="M178" t="n">
         <v>0</v>
       </c>
-      <c r="N178" t="n">
-        <v>0</v>
-      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/988019c539ba46f4899feb6d11e74777/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f0d1ce6b546d4b229428a065734058fd/detail</t>
         </is>
       </c>
       <c r="P178" t="inlineStr"/>
@@ -12896,17 +12184,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>终生禁驾名单信息分页查询服务</t>
+          <t>事故处理点信息数据量查询服务</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>终生禁驾名单信息分页查询服务</t>
+          <t>事故处理点信息数据量查询服务</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -12916,7 +12204,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -12929,9 +12217,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>True</t>
@@ -12943,17 +12229,15 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>28316</v>
+        <v>253</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
       </c>
-      <c r="N179" t="n">
-        <v>0</v>
-      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/989cadd0ecc0478f871c2bd277fb460b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f95585be05834f0aa22792c23eba2d0e/detail</t>
         </is>
       </c>
       <c r="P179" t="inlineStr"/>
@@ -12999,9 +12283,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>0</v>
-      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>True</t>
@@ -13013,14 +12295,12 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="M180" t="n">
         <v>0</v>
       </c>
-      <c r="N180" t="n">
-        <v>0</v>
-      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/1caaeffaea8048b997238938383687f9/detail</t>
@@ -13036,27 +12316,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>全市看守所、拘留所信息分页查询服务</t>
+          <t>医疗保险定点门诊单位信息数据量查询服务</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>全市看守所、拘留所信息分页查询服务</t>
+          <t>医疗保险定点门诊单位信息数据量查询服务</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市人力资源和社会保障局</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-11-26</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13069,9 +12349,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>0</v>
-      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>True</t>
@@ -13083,17 +12361,15 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>418</v>
+        <v>759</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
       </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d59ce1b96b4745f599e4fdca34643bb2/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2a3d0e57e44c43e299796636128ddff4/detail</t>
         </is>
       </c>
       <c r="P181" t="inlineStr"/>
@@ -13106,17 +12382,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>电子监控违法处理岗位信息数据量查询服务</t>
+          <t>非营业性爆破作业单位信息数据量查询服务</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>电子监控违法处理岗位信息数据量查询服务</t>
+          <t>非营业性爆破作业单位信息数据量查询服务</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -13139,9 +12415,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>0</v>
-      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>True</t>
@@ -13153,17 +12427,15 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>11976</v>
+        <v>484</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
       </c>
-      <c r="N182" t="n">
-        <v>0</v>
-      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/da0d237b254446a696f166d9f8ea6ea4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/39e5ecb0b000439ebdf2fb290db34aef/detail</t>
         </is>
       </c>
       <c r="P182" t="inlineStr"/>
@@ -13176,27 +12448,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>派出所信息分页查询服务</t>
+          <t>拟定全市博物馆事业发展规划信息分页查询服务</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>派出所信息分页查询服务</t>
+          <t>拟定全市博物馆事业发展规划信息分页查询服务</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市文化和旅游局</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13206,12 +12478,10 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I183" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>True</t>
@@ -13223,17 +12493,15 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>4016</v>
+        <v>1048</v>
       </c>
       <c r="M183" t="n">
-        <v>1</v>
-      </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e864861f01ae4b90a18ba88b0ea46243/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3ca77a1ceb04467292b9de9b16d24dac/detail</t>
         </is>
       </c>
       <c r="P183" t="inlineStr"/>
@@ -13279,9 +12547,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>0</v>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>True</t>
@@ -13293,14 +12559,12 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M184" t="n">
         <v>1</v>
       </c>
-      <c r="N184" t="n">
-        <v>0</v>
-      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/613725ee4d95499396cca42b3eed5fe2/detail</t>
@@ -13316,27 +12580,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>医疗保险定点门诊单位信息数据量查询服务</t>
+          <t>非营业性爆破作业单位信息分页查询服务</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>医疗保险定点门诊单位信息数据量查询服务</t>
+          <t>非营业性爆破作业单位信息分页查询服务</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>淄博市人力资源和社会保障局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2018-11-26</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13349,9 +12613,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>0</v>
-      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>True</t>
@@ -13363,17 +12625,15 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="M185" t="n">
         <v>0</v>
       </c>
-      <c r="N185" t="n">
-        <v>0</v>
-      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2a3d0e57e44c43e299796636128ddff4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7eddbf42e25c41fdbc1be9629dd72d73/detail</t>
         </is>
       </c>
       <c r="P185" t="inlineStr"/>
@@ -13386,17 +12646,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>非营业性爆破作业单位信息数据量查询服务</t>
+          <t>电子监控违法处理岗位信息分页查询服务</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>非营业性爆破作业单位信息数据量查询服务</t>
+          <t>电子监控违法处理岗位信息分页查询服务</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -13419,9 +12679,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I186" t="n">
-        <v>0</v>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>True</t>
@@ -13433,17 +12691,15 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>474</v>
+        <v>12221</v>
       </c>
       <c r="M186" t="n">
         <v>0</v>
       </c>
-      <c r="N186" t="n">
-        <v>0</v>
-      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/39e5ecb0b000439ebdf2fb290db34aef/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a9f3f44080804d34b563b613e5aafdc5/detail</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -13456,27 +12712,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>拟定全市博物馆事业发展规划信息分页查询服务</t>
+          <t>执法机构统信息分页查询服务</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>拟定全市博物馆事业发展规划信息分页查询服务</t>
+          <t>执法机构统信息分页查询服务</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>淄博市文化和旅游局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2019-01-02</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -13486,12 +12742,10 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>True</t>
@@ -13503,17 +12757,15 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>1043</v>
+        <v>16753</v>
       </c>
       <c r="M187" t="n">
         <v>0</v>
       </c>
-      <c r="N187" t="n">
-        <v>0</v>
-      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3ca77a1ceb04467292b9de9b16d24dac/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b1f28cd0057c4a7b9b098b9618bbd636/detail</t>
         </is>
       </c>
       <c r="P187" t="inlineStr"/>
@@ -13526,17 +12778,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>执法机构统信息分页查询服务</t>
+          <t>终生禁驾名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>执法机构统信息分页查询服务</t>
+          <t>终生禁驾名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -13559,9 +12811,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I188" t="n">
-        <v>0</v>
-      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>True</t>
@@ -13573,17 +12823,15 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>16295</v>
+        <v>31189</v>
       </c>
       <c r="M188" t="n">
         <v>0</v>
       </c>
-      <c r="N188" t="n">
-        <v>0</v>
-      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b1f28cd0057c4a7b9b098b9618bbd636/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c18d20b720e549db8b3c903e92206d18/detail</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -13596,27 +12844,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>终生禁驾名单信息数据量查询服务</t>
+          <t>营业性演出监督检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>终生禁驾名单信息数据量查询服务</t>
+          <t>营业性演出监督检查信息数据量查询服务</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>淄博市公安局</t>
+          <t>淄博市文化市场执法支队</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-01-02</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -13626,12 +12874,10 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>有条件开放</t>
-        </is>
-      </c>
-      <c r="I189" t="n">
-        <v>0</v>
-      </c>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>True</t>
@@ -13643,17 +12889,15 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>30737</v>
+        <v>80</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
       </c>
-      <c r="N189" t="n">
-        <v>0</v>
-      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/c18d20b720e549db8b3c903e92206d18/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c23f25bd7fb64c1c9e1450d6bac9c0d3/detail</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -13666,22 +12910,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>营业性演出监督检查信息数据量查询服务</t>
+          <t>全市看守所、拘留所信息分页查询服务</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>营业性演出监督检查信息数据量查询服务</t>
+          <t>全市看守所、拘留所信息分页查询服务</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>淄博市文化市场执法支队</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -13696,12 +12940,10 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I190" t="n">
-        <v>0</v>
-      </c>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>True</t>
@@ -13713,17 +12955,15 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>77</v>
+        <v>433</v>
       </c>
       <c r="M190" t="n">
         <v>0</v>
       </c>
-      <c r="N190" t="n">
-        <v>0</v>
-      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/c23f25bd7fb64c1c9e1450d6bac9c0d3/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d59ce1b96b4745f599e4fdca34643bb2/detail</t>
         </is>
       </c>
       <c r="P190" t="inlineStr"/>
@@ -13736,17 +12976,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>非营业性爆破作业单位信息分页查询服务</t>
+          <t>电子监控违法处理岗位信息数据量查询服务</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>非营业性爆破作业单位信息分页查询服务</t>
+          <t>电子监控违法处理岗位信息数据量查询服务</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -13769,9 +13009,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>0</v>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>True</t>
@@ -13783,17 +13021,15 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>469</v>
+        <v>12178</v>
       </c>
       <c r="M191" t="n">
         <v>0</v>
       </c>
-      <c r="N191" t="n">
-        <v>0</v>
-      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7eddbf42e25c41fdbc1be9629dd72d73/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/da0d237b254446a696f166d9f8ea6ea4/detail</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -13806,7 +13042,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>全市刻章单位信息数据量查询服务</t>
+          <t>派出所信息分页查询服务</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13816,7 +13052,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>全市刻章单位信息数据量查询服务</t>
+          <t>派出所信息分页查询服务</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -13839,9 +13075,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I192" t="n">
-        <v>0</v>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>True</t>
@@ -13853,17 +13087,15 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>381</v>
+        <v>4222</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1caaeffaea8048b997238938383687f9/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e864861f01ae4b90a18ba88b0ea46243/detail</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
@@ -13876,27 +13108,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>医疗保险定点门诊单位信息数据量查询服务</t>
+          <t>驾驶考试场信息分页查询服务</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>医疗保险定点门诊单位信息数据量查询服务</t>
+          <t>驾驶考试场信息分页查询服务</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>淄博市人力资源和社会保障局</t>
+          <t>淄博市公安局</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2018-11-26</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -13909,9 +13141,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>True</t>
@@ -13923,17 +13153,15 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>554</v>
+        <v>249</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
       </c>
-      <c r="N193" t="n">
-        <v>0</v>
-      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2a3d0e57e44c43e299796636128ddff4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/efa495a3de0e4a6caa9d581a95ba093d/detail</t>
         </is>
       </c>
       <c r="P193" t="inlineStr"/>
